--- a/livrables/marges_par_intergare_GTFS2023.xlsx
+++ b/livrables/marges_par_intergare_GTFS2023.xlsx
@@ -442,7 +442,7 @@
     <col width="22" customWidth="1" min="10" max="10"/>
     <col width="19" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="21" customWidth="1" min="13" max="13"/>
+    <col width="19" customWidth="1" min="13" max="13"/>
     <col width="11" customWidth="1" min="14" max="14"/>
     <col width="21" customWidth="1" min="15" max="15"/>
     <col width="20" customWidth="1" min="16" max="16"/>
@@ -515,7 +515,7 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>t_base_S1cap160_min</t>
+          <t>t_base_cap160_min</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
